--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BB721C4-3F84-054F-A88D-ABDCA9D9BE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E06B6720-8C87-334E-A1A0-0F77BBB8EEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>No.</t>
   </si>
@@ -43,6 +43,15 @@
   </si>
   <si>
     <t>Sisa Uang</t>
+  </si>
+  <si>
+    <t>Kolom1</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Kolom2</t>
   </si>
 </sst>
 </file>
@@ -253,18 +262,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF505050"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF505050"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF505050"/>
@@ -308,6 +305,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color rgb="FF505050"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF505050"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF505050"/>
+        </top>
         <bottom style="thin">
           <color rgb="FF505050"/>
         </bottom>
@@ -315,18 +321,21 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF505050"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF505050"/>
         </left>
         <right style="thin">
           <color rgb="FF505050"/>
         </right>
-        <top style="thin">
-          <color rgb="FF505050"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF505050"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -343,13 +352,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{40327637-4E97-844A-8A7C-573666E9B021}" name="Tabel4" displayName="Tabel4" ref="B3:E28" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{40327637-4E97-844A-8A7C-573666E9B021}" name="Tabel4" displayName="Tabel4" ref="B3:E28" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="B3:E28" xr:uid="{40327637-4E97-844A-8A7C-573666E9B021}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{402F9F97-9CF5-1440-892E-E25BDC9523DA}" name="No." dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{8CD88954-B622-DD4A-A831-E0B2EDA5B06F}" name="Uang Masuk" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{EA97175B-B7B5-F743-A355-468B54B6D909}" name="Uang keluat" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{402F9F97-9CF5-1440-892E-E25BDC9523DA}" name="No." dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{8CD88954-B622-DD4A-A831-E0B2EDA5B06F}" name="Uang Masuk" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{EA97175B-B7B5-F743-A355-468B54B6D909}" name="Uang keluat" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{551D820C-6575-4242-AB96-0664D689AE02}" name="Sisa Uang" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0306E292-D6EF-3F4C-81E1-20514253C70E}" name="Tabel1" displayName="Tabel1" ref="F3:H29" totalsRowShown="0">
+  <autoFilter ref="F3:H29" xr:uid="{0306E292-D6EF-3F4C-81E1-20514253C70E}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{C14F6A67-D794-584D-995F-4540D607BEF9}" name="test"/>
+    <tableColumn id="3" xr3:uid="{942C7CAB-7FCC-BC4E-8007-90E28F8EBAB7}" name="Kolom2"/>
+    <tableColumn id="2" xr3:uid="{49C943C8-1825-AF40-9737-50605BA69042}" name="Kolom1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -672,15 +693,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{035FC864-24C2-974C-9FCB-EB6ABC09A3BF}">
-  <dimension ref="B3:E28"/>
+  <dimension ref="B3:H28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.2578125" customWidth="1"/>
     <col min="4" max="4" width="13.98828125" customWidth="1"/>
     <col min="5" max="5" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.22265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
@@ -693,8 +715,17 @@
       <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -709,7 +740,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B5" s="4">
         <v>2</v>
       </c>
@@ -717,7 +748,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6" s="4">
         <v>3</v>
       </c>
@@ -725,7 +756,7 @@
       <c r="D6" s="1"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7" s="4">
         <v>4</v>
       </c>
@@ -733,7 +764,7 @@
       <c r="D7" s="1"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
         <v>5</v>
       </c>
@@ -741,7 +772,7 @@
       <c r="D8" s="1"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" s="4">
         <v>6</v>
       </c>
@@ -749,7 +780,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="4">
         <v>7</v>
       </c>
@@ -757,7 +788,7 @@
       <c r="D10" s="1"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="4">
         <v>8</v>
       </c>
@@ -765,7 +796,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="4">
         <v>9</v>
       </c>
@@ -773,7 +804,7 @@
       <c r="D12" s="1"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="4">
         <v>10</v>
       </c>
@@ -781,7 +812,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B14" s="4">
         <v>11</v>
       </c>
@@ -789,7 +820,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B15" s="4">
         <v>12</v>
       </c>
@@ -797,7 +828,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B16" s="4">
         <v>13</v>
       </c>
@@ -904,8 +935,9 @@
   </sheetData>
   <phoneticPr fontId="1" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>